--- a/www/flightdata/xlsx/eoss-327.xlsx
+++ b/www/flightdata/xlsx/eoss-327.xlsx
@@ -3699,7 +3699,7 @@
         <v>27902.61</v>
       </c>
       <c r="I2">
-        <v>678</v>
+        <v>480</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
